--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120837476</v>
+        <v>120837423</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>94747</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120837423</v>
+        <v>120837476</v>
       </c>
       <c r="B3" t="n">
-        <v>94737</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122649201</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95011</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långåsarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563255</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6516262</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122649201</v>
       </c>
       <c r="B4" t="n">
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122649201</v>
       </c>
       <c r="B4" t="n">
-        <v>95012</v>
+        <v>95015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122649201</v>
       </c>
       <c r="B4" t="n">
-        <v>95015</v>
+        <v>95118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122649201</v>
       </c>
       <c r="B4" t="n">
-        <v>95118</v>
+        <v>95126</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122649201</v>
       </c>
       <c r="B4" t="n">
-        <v>95126</v>
+        <v>95128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 46644-2024 artfynd.xlsx
+++ b/artfynd/A 46644-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>122649201</v>
       </c>
       <c r="B4" t="n">
-        <v>95128</v>
+        <v>95136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
